--- a/path2shock_calculation/output/path2shock_Base.xlsx
+++ b/path2shock_calculation/output/path2shock_Base.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>13% max</t>
+          <t>(+13 ppts)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>(+198 ppts)</t>
+          <t>198.0% max</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -721,12 +721,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>13 peak</t>
+          <t>(+13 ppts)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>(+216 ppts)</t>
+          <t>216.0 peak</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -749,12 +749,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>13% peak</t>
+          <t>(+1300 bps)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>(+23400 bps)</t>
+          <t>234.0 peak</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -777,12 +777,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>13% peak</t>
+          <t>(+1300 bps)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>(+25200 bps)</t>
+          <t>252.0 peak</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -833,12 +833,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>13% peak</t>
+          <t>(+1300 bps)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>(+37800 bps)</t>
+          <t>378.0 peak</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -861,12 +861,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>13% peak</t>
+          <t>(+1300 bps)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>(+39600 bps)</t>
+          <t>396.0 peak</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -889,12 +889,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>13% peak</t>
+          <t>(+1300 bps)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>(+41400 bps)</t>
+          <t>414.0 peak</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -939,12 +939,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>13% peak</t>
+          <t>(+1300 bps)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>(+45000 bps)</t>
+          <t>450.0 peak</t>
         </is>
       </c>
       <c r="E21" t="n">

--- a/path2shock_calculation/output/path2shock_Base.xlsx
+++ b/path2shock_calculation/output/path2shock_Base.xlsx
@@ -693,7 +693,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>(+13 ppts)</t>
+          <t>(+13.0 ppts)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -721,19 +721,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>(+13 ppts)</t>
+          <t>(+10 ppts)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>216.0 peak</t>
+          <t>213.3 peak</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>13</v>
+        <v>10.40000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>216</v>
+        <v>213.3</v>
       </c>
     </row>
     <row r="14">

--- a/path2shock_calculation/output/path2shock_Base.xlsx
+++ b/path2shock_calculation/output/path2shock_Base.xlsx
@@ -473,12 +473,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20.0 %</t>
+          <t>62.2%*</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>0.2</v>
+        <v>0.6222222222222222</v>
       </c>
       <c r="F2" t="inlineStr"/>
     </row>
@@ -495,12 +495,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.3 %</t>
+          <t>17.4%+</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>0.04347826086956519</v>
+        <v>0.173913043478261</v>
       </c>
       <c r="F3" t="inlineStr"/>
     </row>
@@ -517,12 +517,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.4 %</t>
+          <t>9.8%+</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>0.02439024390243905</v>
+        <v>0.09756097560975618</v>
       </c>
       <c r="F4" t="inlineStr"/>
     </row>
@@ -539,12 +539,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.7 %</t>
+          <t>22.0%#</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>0.01694915254237284</v>
+        <v>0.2203389830508475</v>
       </c>
       <c r="F5" t="inlineStr"/>
     </row>
@@ -561,12 +561,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.3 %</t>
+          <t>16.9%#</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>0.01298701298701288</v>
+        <v>0.1688311688311688</v>
       </c>
       <c r="F6" t="inlineStr"/>
     </row>
@@ -583,12 +583,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.1 %</t>
+          <t>4.1%*</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>0.01052631578947372</v>
+        <v>0.04125465178096754</v>
       </c>
       <c r="F7" t="inlineStr"/>
     </row>
@@ -605,12 +605,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.9 %</t>
+          <t>3.5%*</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>0.008849557522123908</v>
+        <v>0.03479313213826496</v>
       </c>
       <c r="F8" t="inlineStr"/>
     </row>
@@ -627,12 +627,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.8 %</t>
+          <t>3.0%*</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
-        <v>0.007633587786259444</v>
+        <v>0.03008199038733395</v>
       </c>
       <c r="F9" t="inlineStr"/>
     </row>
@@ -649,12 +649,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.7 %</t>
+          <t>2.6%*</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
-        <v>0.006711409395973256</v>
+        <v>0.02649471421678284</v>
       </c>
       <c r="F10" t="inlineStr"/>
     </row>
@@ -833,19 +833,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>(+1300 bps)</t>
+          <t>(100 bps)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>378.0 peak</t>
+          <t>366.0 trough</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>378</v>
+        <v>366</v>
       </c>
     </row>
     <row r="18">
@@ -861,19 +861,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>(+1300 bps)</t>
+          <t>(100 bps)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>396.0 peak</t>
+          <t>384.0 trough</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>396</v>
+        <v>384</v>
       </c>
     </row>
     <row r="19">
@@ -889,19 +889,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>(+1300 bps)</t>
+          <t>(100 bps)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>414.0 peak</t>
+          <t>402.0 trough</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>414</v>
+        <v>402</v>
       </c>
     </row>
     <row r="20">
@@ -917,12 +917,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.2 %</t>
+          <t>1.0%*</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
-        <v>0.002386634844868674</v>
+        <v>0.009501402077444321</v>
       </c>
       <c r="F20" t="inlineStr"/>
     </row>
@@ -939,19 +939,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>(+1300 bps)</t>
+          <t>(100 bps)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>450.0 peak</t>
+          <t>438.0 trough</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>450</v>
+        <v>438</v>
       </c>
     </row>
   </sheetData>
